--- a/assets/Book3.xlsx
+++ b/assets/Book3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreaspapathanasioy/Documents/programming/codes/python/Dashboard-local/Dashboard/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1F5C90-B0B3-4241-AEEA-814C3E469222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4BBF78-9B0A-3D41-ADB8-64CDD78964A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21120" xr2:uid="{2C047A19-3ACC-46EC-BDD5-E3F88895711D}"/>
   </bookViews>
@@ -334,9 +334,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Εισαγωγή" xfId="1" builtinId="20"/>
-    <cellStyle name="Έλεγχος κελιού" xfId="2" builtinId="23"/>
-    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
+    <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
+    <cellStyle name="Input" xfId="1" builtinId="20"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
@@ -425,7 +425,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="el-GR"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -894,7 +894,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="el-GR"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1557,7 +1557,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="el-GR"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1940,7 +1940,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="el-GR"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4828,7 +4828,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Θέμα Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -5147,7 +5147,7 @@
     <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.33203125" customWidth="1"/>
     <col min="23" max="23" width="9.6640625" customWidth="1"/>
-    <col min="24" max="24" width="10.5" customWidth="1"/>
+    <col min="24" max="25" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="17" x14ac:dyDescent="0.25">
@@ -5319,6 +5319,10 @@
         <f>1100</f>
         <v>1100</v>
       </c>
+      <c r="Y2" s="6">
+        <f>700</f>
+        <v>700</v>
+      </c>
     </row>
     <row r="3" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -5413,6 +5417,10 @@
         <f>900+50+500+100</f>
         <v>1550</v>
       </c>
+      <c r="Y3" s="6">
+        <f>400+50+20+30+850+50</f>
+        <v>1400</v>
+      </c>
     </row>
     <row r="4" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -5512,7 +5520,7 @@
       </c>
       <c r="Y4" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="Z4" s="3">
         <f t="shared" si="3"/>
@@ -5705,6 +5713,10 @@
         <f>8+30+6+12+20.4</f>
         <v>76.400000000000006</v>
       </c>
+      <c r="Y8" s="6">
+        <f>10+15</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="9" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -5794,6 +5806,10 @@
         <f>10+16+3</f>
         <v>29</v>
       </c>
+      <c r="Y9" s="6">
+        <f>10</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -5882,6 +5898,10 @@
         <f>115+25</f>
         <v>140</v>
       </c>
+      <c r="Y10" s="6">
+        <f>50+10+15+32</f>
+        <v>107</v>
+      </c>
     </row>
     <row r="11" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -6039,6 +6059,10 @@
         <f>11</f>
         <v>11</v>
       </c>
+      <c r="Y12" s="6">
+        <f>35</f>
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -6184,6 +6208,10 @@
         <f>112+10+800+8+25</f>
         <v>955</v>
       </c>
+      <c r="Y14" s="6">
+        <f>8+40</f>
+        <v>48</v>
+      </c>
     </row>
     <row r="15" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -6256,6 +6284,10 @@
         <f>28</f>
         <v>28</v>
       </c>
+      <c r="Y15" s="6">
+        <f>15+15</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="16" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -6347,6 +6379,10 @@
         <f>60</f>
         <v>60</v>
       </c>
+      <c r="Y16" s="6">
+        <f>60+13</f>
+        <v>73</v>
+      </c>
     </row>
     <row r="17" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -6446,7 +6482,7 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="Z17" s="3">
         <f t="shared" si="4"/>
@@ -6465,6 +6501,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="N18" s="3"/>
+      <c r="Y18" s="3"/>
     </row>
     <row r="20" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -6685,6 +6722,14 @@
         <f>200</f>
         <v>200</v>
       </c>
+      <c r="X22" s="6">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="Y22" s="6">
+        <f>200</f>
+        <v>200</v>
+      </c>
     </row>
     <row r="23" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
@@ -6820,8 +6865,12 @@
         <v>300</v>
       </c>
       <c r="X24" s="6">
-        <f>500+100</f>
-        <v>600</v>
+        <f>500+100-400</f>
+        <v>200</v>
+      </c>
+      <c r="Y24" s="6">
+        <f>250+300</f>
+        <v>550</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6922,7 +6971,7 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="Z25" s="3">
         <f t="shared" si="5"/>
@@ -7036,7 +7085,7 @@
         <v>38</v>
       </c>
       <c r="B29" s="5">
-        <f t="shared" ref="B29:X29" si="6">B25/B17</f>
+        <f t="shared" ref="B29:Y29" si="6">B25/B17</f>
         <v>1.218356572356843</v>
       </c>
       <c r="C29" s="5">
@@ -7126,6 +7175,10 @@
       <c r="X29" s="5">
         <f t="shared" si="6"/>
         <v>0.55970149253731338</v>
+      </c>
+      <c r="Y29" s="5">
+        <f t="shared" si="6"/>
+        <v>2.2865853658536586</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7133,7 +7186,7 @@
         <v>39</v>
       </c>
       <c r="B30" s="5">
-        <f t="shared" ref="B30:X30" si="7">B25/B3</f>
+        <f t="shared" ref="B30:Y30" si="7">B25/B3</f>
         <v>0.5625</v>
       </c>
       <c r="C30" s="5">
@@ -7223,6 +7276,10 @@
       <c r="X30" s="5">
         <f t="shared" si="7"/>
         <v>0.38709677419354838</v>
+      </c>
+      <c r="Y30" s="5">
+        <f t="shared" si="7"/>
+        <v>0.5357142857142857</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7230,7 +7287,7 @@
         <v>40</v>
       </c>
       <c r="B31" s="5">
-        <f t="shared" ref="B31:X31" si="8">B3/B17</f>
+        <f t="shared" ref="B31:Y31" si="8">B3/B17</f>
         <v>2.1659672397454988</v>
       </c>
       <c r="C31" s="5">
@@ -7320,6 +7377,10 @@
       <c r="X31" s="5">
         <f t="shared" si="8"/>
         <v>1.4458955223880596</v>
+      </c>
+      <c r="Y31" s="5">
+        <f t="shared" si="8"/>
+        <v>4.2682926829268295</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">
@@ -7330,7 +7391,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B29:X30">
+  <conditionalFormatting sqref="B29:Y30">
     <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
@@ -7338,7 +7399,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31:X31">
+  <conditionalFormatting sqref="B31:Y31">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThanOrEqual">
       <formula>1</formula>
     </cfRule>

--- a/assets/Book3.xlsx
+++ b/assets/Book3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreaspapathanasioy/Documents/programming/codes/python/Dashboard-local/Dashboard/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4BBF78-9B0A-3D41-ADB8-64CDD78964A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2BCC7A-7DD8-9843-9154-CE2CAFE0FF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21120" xr2:uid="{2C047A19-3ACC-46EC-BDD5-E3F88895711D}"/>
   </bookViews>
@@ -5148,6 +5148,7 @@
     <col min="22" max="22" width="10.33203125" customWidth="1"/>
     <col min="23" max="23" width="9.6640625" customWidth="1"/>
     <col min="24" max="25" width="10.5" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="17" x14ac:dyDescent="0.25">
@@ -5323,6 +5324,10 @@
         <f>700</f>
         <v>700</v>
       </c>
+      <c r="Z2" s="6">
+        <f>1400</f>
+        <v>1400</v>
+      </c>
     </row>
     <row r="3" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -5421,6 +5426,10 @@
         <f>400+50+20+30+850+50</f>
         <v>1400</v>
       </c>
+      <c r="Z3" s="6">
+        <f>400</f>
+        <v>400</v>
+      </c>
     </row>
     <row r="4" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -5524,7 +5533,7 @@
       </c>
       <c r="Z4" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" si="3"/>
@@ -5537,6 +5546,7 @@
     </row>
     <row r="5" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="J5" s="3"/>
+      <c r="Z5" s="3"/>
     </row>
     <row r="7" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -5807,6 +5817,10 @@
         <v>29</v>
       </c>
       <c r="Y9" s="6">
+        <f>10+7</f>
+        <v>17</v>
+      </c>
+      <c r="Z9" s="6">
         <f>10</f>
         <v>10</v>
       </c>
@@ -6063,6 +6077,10 @@
         <f>35</f>
         <v>35</v>
       </c>
+      <c r="Z12" s="6">
+        <f>74</f>
+        <v>74</v>
+      </c>
     </row>
     <row r="13" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -6209,8 +6227,8 @@
         <v>955</v>
       </c>
       <c r="Y14" s="6">
-        <f>8+40</f>
-        <v>48</v>
+        <f>8+40+7.5</f>
+        <v>55.5</v>
       </c>
     </row>
     <row r="15" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6482,11 +6500,11 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="4"/>
-        <v>328</v>
+        <v>342.5</v>
       </c>
       <c r="Z17" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AA17" s="3">
         <f t="shared" si="4"/>
@@ -6502,6 +6520,7 @@
       <c r="K18" s="3"/>
       <c r="N18" s="3"/>
       <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
     </row>
     <row r="20" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -6727,8 +6746,8 @@
         <v>400</v>
       </c>
       <c r="Y22" s="6">
-        <f>200</f>
-        <v>200</v>
+        <f>200+300</f>
+        <v>500</v>
       </c>
     </row>
     <row r="23" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6869,8 +6888,8 @@
         <v>200</v>
       </c>
       <c r="Y24" s="6">
-        <f>250+300</f>
-        <v>550</v>
+        <f>250+300-300</f>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6990,6 +7009,7 @@
       <c r="J26" s="3"/>
       <c r="L26" s="3"/>
       <c r="Q26" s="3"/>
+      <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="J27" s="3"/>
@@ -7178,7 +7198,7 @@
       </c>
       <c r="Y29" s="5">
         <f t="shared" si="6"/>
-        <v>2.2865853658536586</v>
+        <v>2.1897810218978102</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7380,7 +7400,7 @@
       </c>
       <c r="Y31" s="5">
         <f t="shared" si="8"/>
-        <v>4.2682926829268295</v>
+        <v>4.0875912408759127</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">

--- a/assets/Book3.xlsx
+++ b/assets/Book3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreaspapathanasioy/Documents/programming/codes/python/Dashboard-local/Dashboard/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2BCC7A-7DD8-9843-9154-CE2CAFE0FF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D97D74-E08A-1941-90CB-60CF79B1D781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21120" xr2:uid="{2C047A19-3ACC-46EC-BDD5-E3F88895711D}"/>
   </bookViews>
@@ -5427,8 +5427,8 @@
         <v>1400</v>
       </c>
       <c r="Z3" s="6">
-        <f>400</f>
-        <v>400</v>
+        <f>400+1000+20</f>
+        <v>1420</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="Z4" s="3">
         <f t="shared" si="3"/>
-        <v>-1000</v>
+        <v>20</v>
       </c>
       <c r="AA4" s="3">
         <f t="shared" si="3"/>
@@ -5727,6 +5727,10 @@
         <f>10+15</f>
         <v>25</v>
       </c>
+      <c r="Z8" s="6">
+        <f>18</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -5821,8 +5825,8 @@
         <v>17</v>
       </c>
       <c r="Z9" s="6">
-        <f>10</f>
-        <v>10</v>
+        <f>10+8</f>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5916,6 +5920,10 @@
         <f>50+10+15+32</f>
         <v>107</v>
       </c>
+      <c r="Z10" s="6">
+        <f>8.6</f>
+        <v>8.6</v>
+      </c>
     </row>
     <row r="11" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -5993,6 +6001,10 @@
         <f>5+6</f>
         <v>11</v>
       </c>
+      <c r="Z11" s="6">
+        <f>10+20+3</f>
+        <v>33</v>
+      </c>
     </row>
     <row r="12" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -6078,8 +6090,8 @@
         <v>35</v>
       </c>
       <c r="Z12" s="6">
-        <f>74</f>
-        <v>74</v>
+        <f>74+18+10</f>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -6230,6 +6242,10 @@
         <f>8+40+7.5</f>
         <v>55.5</v>
       </c>
+      <c r="Z14" s="6">
+        <f>10</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:28" s="6" customFormat="1" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -6401,6 +6417,10 @@
         <f>60+13</f>
         <v>73</v>
       </c>
+      <c r="Z16" s="6">
+        <f>11+22+11+22.25</f>
+        <v>66.25</v>
+      </c>
     </row>
     <row r="17" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -6504,7 +6524,7 @@
       </c>
       <c r="Z17" s="3">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>255.85</v>
       </c>
       <c r="AA17" s="3">
         <f t="shared" si="4"/>
@@ -6891,6 +6911,10 @@
         <f>250+300-300</f>
         <v>250</v>
       </c>
+      <c r="Z24" s="6">
+        <f>200+1000</f>
+        <v>1200</v>
+      </c>
     </row>
     <row r="25" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -6994,7 +7018,7 @@
       </c>
       <c r="Z25" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AA25" s="3">
         <f t="shared" si="5"/>
@@ -7105,7 +7129,7 @@
         <v>38</v>
       </c>
       <c r="B29" s="5">
-        <f t="shared" ref="B29:Y29" si="6">B25/B17</f>
+        <f t="shared" ref="B29:Z29" si="6">B25/B17</f>
         <v>1.218356572356843</v>
       </c>
       <c r="C29" s="5">
@@ -7199,6 +7223,10 @@
       <c r="Y29" s="5">
         <f t="shared" si="6"/>
         <v>2.1897810218978102</v>
+      </c>
+      <c r="Z29" s="5">
+        <f t="shared" si="6"/>
+        <v>4.6902481923001762</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7206,7 +7234,7 @@
         <v>39</v>
       </c>
       <c r="B30" s="5">
-        <f t="shared" ref="B30:Y30" si="7">B25/B3</f>
+        <f t="shared" ref="B30:Z30" si="7">B25/B3</f>
         <v>0.5625</v>
       </c>
       <c r="C30" s="5">
@@ -7300,6 +7328,10 @@
       <c r="Y30" s="5">
         <f t="shared" si="7"/>
         <v>0.5357142857142857</v>
+      </c>
+      <c r="Z30" s="5">
+        <f t="shared" si="7"/>
+        <v>0.84507042253521125</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7307,7 +7339,7 @@
         <v>40</v>
       </c>
       <c r="B31" s="5">
-        <f t="shared" ref="B31:Y31" si="8">B3/B17</f>
+        <f t="shared" ref="B31:Z31" si="8">B3/B17</f>
         <v>2.1659672397454988</v>
       </c>
       <c r="C31" s="5">
@@ -7401,6 +7433,10 @@
       <c r="Y31" s="5">
         <f t="shared" si="8"/>
         <v>4.0875912408759127</v>
+      </c>
+      <c r="Z31" s="5">
+        <f t="shared" si="8"/>
+        <v>5.5501270275552086</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="16" thickTop="1" x14ac:dyDescent="0.2">
@@ -7411,7 +7447,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B29:Y30">
+  <conditionalFormatting sqref="B29:Z30">
     <cfRule type="cellIs" dxfId="9" priority="4" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
@@ -7419,7 +7455,7 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31:Y31">
+  <conditionalFormatting sqref="B31:Z31">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThanOrEqual">
       <formula>1</formula>
     </cfRule>
